--- a/data/gravel/Otso Fenrir Steel (long) 2025.xlsx
+++ b/data/gravel/Otso Fenrir Steel (long) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F275CE1-1F3C-AF47-BB0A-D369BDEFA051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20AA0E1-4FEA-1C4D-861C-BE54F578D274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="980" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -1454,9 +1454,7 @@
       <c r="A44" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>94</v>
-      </c>
+      <c r="B44" s="1"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">

--- a/data/gravel/Otso Fenrir Steel (long) 2025.xlsx
+++ b/data/gravel/Otso Fenrir Steel (long) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20AA0E1-4FEA-1C4D-861C-BE54F578D274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06AF509F-24A8-FA43-948D-FE4654C2B779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="980" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -369,6 +369,9 @@
       </rPr>
       <t>h</t>
     </r>
+  </si>
+  <si>
+    <t>https://otsocycles.com/cdn/shop/files/fenrir_stainless_slider_1.jpg?v=1725541452&amp;width=1800</t>
   </si>
 </sst>
 </file>
@@ -768,6 +771,11 @@
         <v>100</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>108</v>
+      </c>
+    </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>

--- a/data/gravel/Otso Fenrir Steel (long) 2025.xlsx
+++ b/data/gravel/Otso Fenrir Steel (long) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06AF509F-24A8-FA43-948D-FE4654C2B779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52372EA-0F27-E347-ABCB-0F5AB1653B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10220" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,15 @@
   </si>
   <si>
     <t>https://otsocycles.com/cdn/shop/files/fenrir_stainless_slider_1.jpg?v=1725541452&amp;width=1800</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Burnsville, Minnesota, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -725,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1627,11 +1636,17 @@
       <c r="A69" t="s">
         <v>88</v>
       </c>
+      <c r="B69">
+        <v>2550</v>
+      </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>89</v>
       </c>
+      <c r="B70">
+        <v>3700</v>
+      </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
@@ -1641,6 +1656,17 @@
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>91</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>109</v>
+      </c>
+      <c r="B73" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Otso Fenrir Steel (long) 2025.xlsx
+++ b/data/gravel/Otso Fenrir Steel (long) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E92352F-0C74-A245-A5F5-B7F1975C733B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73570188-D970-6D4E-B3D4-7009FBA73803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17860" yWindow="-18120" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="131">
   <si>
     <t>brand</t>
   </si>
@@ -408,6 +408,24 @@
   </si>
   <si>
     <t>a8:g34</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -754,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1901,111 +1919,99 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>65</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>67</v>
-      </c>
-      <c r="B53">
-        <v>31.6</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>68</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>69</v>
-      </c>
-      <c r="B55">
-        <v>40</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>71</v>
+        <v>65</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>73</v>
+        <v>67</v>
+      </c>
+      <c r="B59">
+        <v>31.6</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>74</v>
+        <v>68</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>75</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>90</v>
+        <v>69</v>
+      </c>
+      <c r="B61">
+        <v>40</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>78</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>79</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>80</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>90</v>
@@ -2013,62 +2019,104 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>82</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>83</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>84</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>90</v>
+        <v>78</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B71">
-        <v>2550</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>86</v>
-      </c>
-      <c r="B72">
-        <v>3700</v>
+        <v>80</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>87</v>
+        <v>81</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>100</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>101</v>
       </c>
     </row>

--- a/data/gravel/Otso Fenrir Steel (long) 2025.xlsx
+++ b/data/gravel/Otso Fenrir Steel (long) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73570188-D970-6D4E-B3D4-7009FBA73803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B2493F-1993-7C4D-82EB-9C36C69FAC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17860" yWindow="-18120" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="133">
   <si>
     <t>brand</t>
   </si>
@@ -407,9 +407,6 @@
     <t>Fenrir Stainless (long)</t>
   </si>
   <si>
-    <t>a8:g34</t>
-  </si>
-  <si>
     <t>head_tube_d</t>
   </si>
   <si>
@@ -426,6 +423,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>a8:g36</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
   </si>
 </sst>
 </file>
@@ -772,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -828,7 +834,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -1608,460 +1614,484 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>42</v>
+      <c r="A26" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>43</v>
+      <c r="A27" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>45</v>
-      </c>
-      <c r="F29">
-        <v>2580</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30">
-        <v>700</v>
-      </c>
-      <c r="D30">
-        <v>700</v>
-      </c>
-      <c r="E30">
-        <v>700</v>
-      </c>
-      <c r="F30">
-        <v>700</v>
-      </c>
-      <c r="G30">
-        <v>700</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31">
-        <v>2.35</v>
-      </c>
-      <c r="D31">
-        <v>2.35</v>
-      </c>
-      <c r="E31">
-        <v>2.35</v>
+        <v>45</v>
       </c>
       <c r="F31">
-        <v>2.35</v>
-      </c>
-      <c r="G31">
-        <v>2.35</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C32">
-        <v>2.2999999999999998</v>
+        <v>700</v>
       </c>
       <c r="D32">
-        <v>2.2999999999999998</v>
+        <v>700</v>
       </c>
       <c r="E32">
-        <v>2.2999999999999998</v>
+        <v>700</v>
       </c>
       <c r="F32">
-        <v>2.2999999999999998</v>
+        <v>700</v>
       </c>
       <c r="G32">
-        <v>2.2999999999999998</v>
+        <v>700</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33">
+        <v>2.35</v>
+      </c>
+      <c r="D33">
+        <v>2.35</v>
+      </c>
+      <c r="E33">
+        <v>2.35</v>
+      </c>
+      <c r="F33">
+        <v>2.35</v>
+      </c>
+      <c r="G33">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D34">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E34">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F34">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G34">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>49</v>
       </c>
-      <c r="C33">
-        <f>C35*2.54</f>
+      <c r="C35">
+        <f>C37*2.54</f>
         <v>147.32</v>
       </c>
-      <c r="D33">
-        <f t="shared" ref="D33:G34" si="10">D35*2.54</f>
+      <c r="D35">
+        <f t="shared" ref="D35:G36" si="10">D37*2.54</f>
         <v>160.02000000000001</v>
       </c>
-      <c r="E33">
+      <c r="E35">
         <f t="shared" si="10"/>
         <v>170.18</v>
       </c>
-      <c r="F33">
+      <c r="F35">
         <f t="shared" si="10"/>
         <v>180.34</v>
       </c>
-      <c r="G33">
+      <c r="G35">
         <f t="shared" si="10"/>
         <v>190.5</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>50</v>
       </c>
-      <c r="C34">
-        <f>C36*2.54</f>
+      <c r="C36">
+        <f>C38*2.54</f>
         <v>162.56</v>
       </c>
-      <c r="D34">
+      <c r="D36">
         <f t="shared" si="10"/>
         <v>170.18</v>
       </c>
-      <c r="E34">
+      <c r="E36">
         <f t="shared" si="10"/>
         <v>180.34</v>
       </c>
-      <c r="F34">
+      <c r="F36">
         <f t="shared" si="10"/>
         <v>190.5</v>
       </c>
-      <c r="G34">
+      <c r="G36">
         <f t="shared" si="10"/>
         <v>198.12</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="C35" s="2">
+    <row r="37" spans="1:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="C37" s="2">
         <v>58</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D37" s="2">
         <v>63</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E37" s="2">
         <v>67</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F37" s="2">
         <v>71</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G37" s="2">
         <v>75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36">
-        <v>64</v>
-      </c>
-      <c r="D36">
-        <v>67</v>
-      </c>
-      <c r="E36">
-        <v>71</v>
-      </c>
-      <c r="F36">
-        <v>75</v>
-      </c>
-      <c r="G36">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>92</v>
-      </c>
-      <c r="B37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" t="s">
-        <v>112</v>
-      </c>
-      <c r="D37" t="s">
-        <v>114</v>
-      </c>
-      <c r="E37" t="s">
-        <v>115</v>
-      </c>
-      <c r="F37" t="s">
-        <v>116</v>
-      </c>
-      <c r="G37" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>94</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H38" t="s">
-        <v>113</v>
+        <v>51</v>
+      </c>
+      <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38">
+        <v>64</v>
+      </c>
+      <c r="D38">
+        <v>67</v>
+      </c>
+      <c r="E38">
+        <v>71</v>
+      </c>
+      <c r="F38">
+        <v>75</v>
+      </c>
+      <c r="G38">
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>95</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
+      </c>
+      <c r="B39" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" t="s">
+        <v>114</v>
+      </c>
+      <c r="E39" t="s">
+        <v>115</v>
+      </c>
+      <c r="F39" t="s">
+        <v>116</v>
+      </c>
+      <c r="G39" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>53</v>
-      </c>
-      <c r="B40" t="s">
-        <v>54</v>
+        <v>94</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H40" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>56</v>
-      </c>
-      <c r="B42">
-        <v>20</v>
+        <v>53</v>
+      </c>
+      <c r="B42" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>57</v>
-      </c>
-      <c r="B43">
-        <v>2.6</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>121</v>
+        <v>55</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B44">
-        <v>2.8</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B45">
-        <v>120</v>
+        <v>2.6</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>60</v>
-      </c>
-      <c r="B46" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="B46">
+        <v>2.8</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>61</v>
+        <v>59</v>
+      </c>
+      <c r="B47">
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>62</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B48" s="1"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B49">
-        <v>148</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>64</v>
-      </c>
-      <c r="B50">
-        <v>110</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>125</v>
+        <v>63</v>
+      </c>
+      <c r="B51">
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>126</v>
+        <v>64</v>
+      </c>
+      <c r="B52">
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>65</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>66</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>67</v>
-      </c>
-      <c r="B59">
-        <v>31.6</v>
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>68</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B61">
-        <v>40</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>71</v>
+        <v>69</v>
+      </c>
+      <c r="B63">
+        <v>40</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>75</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>77</v>
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>78</v>
-      </c>
-      <c r="B70">
-        <v>2</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>79</v>
-      </c>
-      <c r="B71">
-        <v>1</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>80</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>90</v>
+        <v>78</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>81</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>90</v>
@@ -2069,7 +2099,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>90</v>
@@ -2077,7 +2107,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>90</v>
@@ -2085,38 +2115,54 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B77">
-        <v>2550</v>
+        <v>83</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>86</v>
-      </c>
-      <c r="B78">
-        <v>3700</v>
+        <v>84</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>87</v>
+        <v>85</v>
+      </c>
+      <c r="B79">
+        <v>2550</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>88</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>99</v>
+        <v>86</v>
+      </c>
+      <c r="B80">
+        <v>3700</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>100</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B83" t="s">
         <v>101</v>
       </c>
     </row>
